--- a/public/templates/attendance_template.xlsx
+++ b/public/templates/attendance_template.xlsx
@@ -57,7 +57,7 @@
     <t>20日</t>
   </si>
   <si>
-    <t>○＝終日、△＝半日（0.5日）。有休の午前半休は3.5時間、午後半休は4.0時間。B-2は09:00–18:00（休憩1時間、実働8.0h、午前3.5h・午後4.5h）。Dは08:30–12:30（実働4.0h）。超え勤務は所定の始業前・終業後に在籍した分。</t>
+    <t>○＝終日、△＝半日（0.5日）。有休の午前半休は3.5時間、午後半休は4.0時間。日勤 (8H) は09:00–18:00（休憩1時間、実働8.0h）。半日 (4H) は08:30–12:30（実働4.0h）。所定が8時間の日は日勤、4時間の日は半日の列に印を付けます。超え勤務は所定の始業前・終業後に在籍した分。</t>
   </si>
   <si>
     <t>曜</t>
@@ -66,7 +66,7 @@
     <t>休暇・区分</t>
   </si>
   <si>
-    <t>勤務記号</t>
+    <t>勤務</t>
   </si>
   <si>
     <t>時間外・休日</t>
@@ -90,12 +90,12 @@
     <t>有休</t>
   </si>
   <si>
-    <t xml:space="preserve">B-2
+    <t xml:space="preserve">日勤
 (8H)</t>
   </si>
   <si>
-    <t xml:space="preserve">D
-(4H木土)</t>
+    <t xml:space="preserve">半日
+(4H)</t>
   </si>
   <si>
     <t>始業</t>
@@ -140,14 +140,15 @@
     <t>リハビリフルタイムパート</t>
   </si>
   <si>
-    <t>○＝終日、△＝半日（0.5日）。有休の午前半休は3.5時間、午後半休は4.0時間。A-1は08:30–17:30（休憩1時間、実働8.0h、午前3.5h・午後4.5h）。Dは08:30–12:30（実働4.0h）。7.5Hは08:30–17:00（休憩1時間、実働7.5h、午前3.5h・午後4.0h）。超え勤務は所定の始業前・終業後に在籍した分。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-1
+    <t>○＝終日、△＝半日（0.5日）。有休の午前半休は3.5時間、午後半休は4.0時間。フル (8H) は08:30–17:30（休憩1時間、実働8.0h）。日勤 (7.5H) は08:30–17:00（休憩1時間、実働7.5h）。半日 (4H) は08:30–12:30（実働4.0h）。所定時間に合う列へ印を付けます。超え勤務は所定の始業前・終業後に在籍した分。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フル
 (8H)</t>
   </si>
   <si>
-    <t>7.5H</t>
+    <t xml:space="preserve">日勤
+(7.5H)</t>
   </si>
 </sst>
 </file>
@@ -805,8 +806,7 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
     <col min="3" max="6" width="7" customWidth="1"/>
-    <col min="7" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="7" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="28" customWidth="1"/>
@@ -1640,8 +1640,7 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
     <col min="3" max="6" width="7" customWidth="1"/>
-    <col min="7" max="9" width="11" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="7" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>

--- a/public/templates/attendance_template.xlsx
+++ b/public/templates/attendance_template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
   <si>
     <t>出勤簿</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>半日未満（回）</t>
+  </si>
+  <si>
+    <t>勤務時間合計</t>
+  </si>
+  <si>
+    <t>有休時間合計</t>
+  </si>
+  <si>
+    <t>支給対象時間</t>
   </si>
   <si>
     <t>リハビリフルタイムパート</t>
@@ -800,7 +809,7 @@
     <tabColor rgb="FF0F5C61"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1581,24 +1590,75 @@
       <c r="M47" s="19"/>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="22"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="19"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="19"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="19"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
@@ -1618,6 +1678,9 @@
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
@@ -1634,7 +1697,7 @@
     <tabColor rgb="FF0F5C61"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1685,7 +1748,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1738,7 +1801,7 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1800,13 +1863,13 @@
         <v>23</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>26</v>
@@ -2463,25 +2526,79 @@
       <c r="N47" s="19"/>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="22"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="19"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="19"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="19"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
@@ -2501,6 +2618,9 @@
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>

--- a/public/templates/attendance_template.xlsx
+++ b/public/templates/attendance_template.xlsx
@@ -1684,7 +1684,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L勤怠クラフト&amp;C&amp;A&amp;R&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -2624,7 +2624,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L勤怠クラフト&amp;C&amp;A&amp;R&amp;P / &amp;N</oddFooter>
   </headerFooter>

--- a/public/templates/attendance_template.xlsx
+++ b/public/templates/attendance_template.xlsx
@@ -251,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -335,21 +335,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF9AA5A6"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1F2937"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9AA5A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9AA5A6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF1F2937"/>
       </left>
@@ -379,26 +364,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9AA5A6"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1F2937"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9AA5A6"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1F2937"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -443,28 +413,22 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1485,7 +1449,7 @@
       <c r="J41" s="18"/>
       <c r="K41" s="18"/>
       <c r="L41" s="18"/>
-      <c r="M41" s="19"/>
+      <c r="M41" s="18"/>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
@@ -1502,7 +1466,7 @@
       <c r="J42" s="18"/>
       <c r="K42" s="18"/>
       <c r="L42" s="18"/>
-      <c r="M42" s="19"/>
+      <c r="M42" s="18"/>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
@@ -1519,7 +1483,7 @@
       <c r="J43" s="18"/>
       <c r="K43" s="18"/>
       <c r="L43" s="18"/>
-      <c r="M43" s="19"/>
+      <c r="M43" s="18"/>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
@@ -1536,7 +1500,7 @@
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
       <c r="L44" s="18"/>
-      <c r="M44" s="19"/>
+      <c r="M44" s="18"/>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
@@ -1553,7 +1517,7 @@
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
       <c r="L45" s="18"/>
-      <c r="M45" s="19"/>
+      <c r="M45" s="18"/>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
@@ -1570,7 +1534,7 @@
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
       <c r="L46" s="18"/>
-      <c r="M46" s="19"/>
+      <c r="M46" s="18"/>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
@@ -1587,7 +1551,7 @@
       <c r="J47" s="18"/>
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
-      <c r="M47" s="19"/>
+      <c r="M47" s="18"/>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
@@ -1604,7 +1568,7 @@
       <c r="J48" s="18"/>
       <c r="K48" s="18"/>
       <c r="L48" s="18"/>
-      <c r="M48" s="19"/>
+      <c r="M48" s="18"/>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
@@ -1621,7 +1585,7 @@
       <c r="J49" s="18"/>
       <c r="K49" s="18"/>
       <c r="L49" s="18"/>
-      <c r="M49" s="19"/>
+      <c r="M49" s="18"/>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
@@ -1638,27 +1602,27 @@
       <c r="J50" s="18"/>
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
-      <c r="M50" s="19"/>
+      <c r="M50" s="18"/>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="22"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="33">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
@@ -1671,16 +1635,27 @@
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:M41"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:M42"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:M43"/>
     <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:M44"/>
     <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:M45"/>
     <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:M46"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:M47"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:M48"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:M49"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:M50"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:M51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
@@ -2415,7 +2390,7 @@
       <c r="K41" s="18"/>
       <c r="L41" s="18"/>
       <c r="M41" s="18"/>
-      <c r="N41" s="19"/>
+      <c r="N41" s="18"/>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
@@ -2433,7 +2408,7 @@
       <c r="K42" s="18"/>
       <c r="L42" s="18"/>
       <c r="M42" s="18"/>
-      <c r="N42" s="19"/>
+      <c r="N42" s="18"/>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
@@ -2451,7 +2426,7 @@
       <c r="K43" s="18"/>
       <c r="L43" s="18"/>
       <c r="M43" s="18"/>
-      <c r="N43" s="19"/>
+      <c r="N43" s="18"/>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
@@ -2469,7 +2444,7 @@
       <c r="K44" s="18"/>
       <c r="L44" s="18"/>
       <c r="M44" s="18"/>
-      <c r="N44" s="19"/>
+      <c r="N44" s="18"/>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
@@ -2487,7 +2462,7 @@
       <c r="K45" s="18"/>
       <c r="L45" s="18"/>
       <c r="M45" s="18"/>
-      <c r="N45" s="19"/>
+      <c r="N45" s="18"/>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
@@ -2505,7 +2480,7 @@
       <c r="K46" s="18"/>
       <c r="L46" s="18"/>
       <c r="M46" s="18"/>
-      <c r="N46" s="19"/>
+      <c r="N46" s="18"/>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
@@ -2523,7 +2498,7 @@
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
       <c r="M47" s="18"/>
-      <c r="N47" s="19"/>
+      <c r="N47" s="18"/>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
@@ -2541,7 +2516,7 @@
       <c r="K48" s="18"/>
       <c r="L48" s="18"/>
       <c r="M48" s="18"/>
-      <c r="N48" s="19"/>
+      <c r="N48" s="18"/>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
@@ -2559,7 +2534,7 @@
       <c r="K49" s="18"/>
       <c r="L49" s="18"/>
       <c r="M49" s="18"/>
-      <c r="N49" s="19"/>
+      <c r="N49" s="18"/>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
@@ -2577,28 +2552,28 @@
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
       <c r="M50" s="18"/>
-      <c r="N50" s="19"/>
+      <c r="N50" s="18"/>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="22"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="33">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
@@ -2611,16 +2586,27 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:N41"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:N42"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:N43"/>
     <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:N44"/>
     <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:N45"/>
     <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:N46"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:N47"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:N48"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:N49"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:N50"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:N51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
